--- a/src/views/game/zlzq/cardList/guyueCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/guyueCard/z_level.xlsx
@@ -9,11 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14625" windowHeight="10500" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="14400" windowHeight="11190" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="禅意" sheetId="6" r:id="rId1"/>
-    <sheet name="冬神" sheetId="10" r:id="rId2"/>
+    <sheet name="冬神" sheetId="10" r:id="rId1"/>
+    <sheet name="禅意" sheetId="6" r:id="rId2"/>
     <sheet name="帝国" sheetId="8" r:id="rId3"/>
     <sheet name="隐秘" sheetId="12" r:id="rId4"/>
     <sheet name="古月" sheetId="11" r:id="rId5"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="72">
   <si>
     <t>名称</t>
   </si>
@@ -47,22 +47,79 @@
     <t>卡等</t>
   </si>
   <si>
+    <t>骨爆</t>
+  </si>
+  <si>
+    <t>寒风草人1</t>
+  </si>
+  <si>
+    <t>寒风草人2</t>
+  </si>
+  <si>
+    <t>阴冷墓穴</t>
+  </si>
+  <si>
+    <t>神庙魔像</t>
+  </si>
+  <si>
+    <t>极地狂信者</t>
+  </si>
+  <si>
+    <t>灵魂抽取</t>
+  </si>
+  <si>
+    <t>小计：</t>
+  </si>
+  <si>
+    <t>蓝色卡等：</t>
+  </si>
+  <si>
+    <t>冬夜使者</t>
+  </si>
+  <si>
+    <t>寒盲刀客</t>
+  </si>
+  <si>
+    <t>冬幕骑士</t>
+  </si>
+  <si>
+    <t>冰峰甲虫</t>
+  </si>
+  <si>
+    <t>咒杀酷吏</t>
+  </si>
+  <si>
+    <t>紫色卡等：</t>
+  </si>
+  <si>
+    <t>荒芜冰巫·野</t>
+  </si>
+  <si>
+    <t>寒风血刃</t>
+  </si>
+  <si>
+    <t>永夜女王</t>
+  </si>
+  <si>
+    <t>橙色卡等：</t>
+  </si>
+  <si>
+    <t>总计：</t>
+  </si>
+  <si>
+    <t>冬神卡等：</t>
+  </si>
+  <si>
     <t>雪庐草人1</t>
   </si>
   <si>
     <t>雪庐草人2</t>
   </si>
   <si>
-    <t>太极剑法</t>
-  </si>
-  <si>
     <t>连击</t>
   </si>
   <si>
-    <t>小计：</t>
-  </si>
-  <si>
-    <t>蓝色卡等：</t>
+    <t>当铺掌柜</t>
   </si>
   <si>
     <t>雪山飞狐</t>
@@ -71,16 +128,16 @@
     <t>百刺浪客</t>
   </si>
   <si>
-    <t>白鹿贤士</t>
-  </si>
-  <si>
     <t>萌化术</t>
   </si>
   <si>
     <t>渡船隐士</t>
   </si>
   <si>
-    <t>紫色卡等：</t>
+    <t>万物之灵1</t>
+  </si>
+  <si>
+    <t>万物之灵2</t>
   </si>
   <si>
     <t>流岚刃·琳</t>
@@ -95,85 +152,28 @@
     <t>悟能禅杖</t>
   </si>
   <si>
-    <t>逍遥居士·铭</t>
-  </si>
-  <si>
     <t>豪情禅师·悟能</t>
   </si>
   <si>
-    <t>橙色卡等：</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
     <t>禅意卡等：</t>
   </si>
   <si>
-    <t>骨爆</t>
-  </si>
-  <si>
-    <t>转化仪式</t>
-  </si>
-  <si>
-    <t>寒风草人</t>
-  </si>
-  <si>
-    <t>寒冬将至1</t>
-  </si>
-  <si>
-    <t>寒冬将至2</t>
-  </si>
-  <si>
-    <t>神庙魔像</t>
-  </si>
-  <si>
-    <t>极地狂信者</t>
-  </si>
-  <si>
-    <t>灵魂抽取</t>
-  </si>
-  <si>
-    <t>寒盲刀客</t>
-  </si>
-  <si>
-    <t>冬幕骑士</t>
-  </si>
-  <si>
-    <t>冰峰甲虫</t>
-  </si>
-  <si>
-    <t>寒风血刃</t>
-  </si>
-  <si>
-    <t>不息之灵</t>
-  </si>
-  <si>
-    <t>永夜女王</t>
-  </si>
-  <si>
-    <t>寒风魔将·塞古斯</t>
-  </si>
-  <si>
-    <t>冬神卡等：</t>
-  </si>
-  <si>
     <t>圣殿斥候</t>
   </si>
   <si>
-    <t>天使琼浆</t>
-  </si>
-  <si>
     <t>炫目神光1</t>
   </si>
   <si>
     <t>炫目神光2</t>
   </si>
   <si>
-    <t>炫目神光3</t>
-  </si>
-  <si>
-    <t>塔楼弓手</t>
+    <t>天使琼浆1</t>
+  </si>
+  <si>
+    <t>天使琼浆2</t>
+  </si>
+  <si>
+    <t>圣殿卫士</t>
   </si>
   <si>
     <t>增援战线</t>
@@ -185,21 +185,18 @@
     <t>田园守望者2</t>
   </si>
   <si>
-    <t>光明惩戒1</t>
-  </si>
-  <si>
-    <t>光明惩戒2</t>
+    <t>光明惩戒</t>
   </si>
   <si>
     <t>召集护卫</t>
   </si>
   <si>
+    <t>惩戒天使</t>
+  </si>
+  <si>
     <t>曙光·安娜贝尔</t>
   </si>
   <si>
-    <t>圣枪·卡洛琳</t>
-  </si>
-  <si>
     <t>明日之音·露娜</t>
   </si>
   <si>
@@ -215,10 +212,10 @@
     <t>学仆-观测型2</t>
   </si>
   <si>
-    <t>沉重否定</t>
-  </si>
-  <si>
-    <t>全数否定</t>
+    <t>沉重否定1</t>
+  </si>
+  <si>
+    <t>沉重否定2</t>
   </si>
   <si>
     <t>隐形术</t>
@@ -233,19 +230,19 @@
     <t>克隆术2</t>
   </si>
   <si>
+    <t>克隆术3</t>
+  </si>
+  <si>
     <t>学仆-脉冲型1</t>
   </si>
   <si>
     <t>学仆-脉冲型2</t>
   </si>
   <si>
-    <t>学仆-脉冲型3</t>
-  </si>
-  <si>
-    <t>符文·邪月之夜</t>
-  </si>
-  <si>
-    <t>学仆-塑钢型</t>
+    <t>符文·邪月之夜1</t>
+  </si>
+  <si>
+    <t>符文·邪月之夜2</t>
   </si>
   <si>
     <t>米拉方舟</t>
@@ -1245,7 +1242,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1256,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1267,7 +1264,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1275,77 +1272,77 @@
         <v>6</v>
       </c>
       <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
         <v>3</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C6" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>23</v>
+      </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3</v>
       </c>
       <c r="C8" s="1">
-        <f>AVERAGE(C2:C5)</f>
-        <v>21.5</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
-        <v>4</v>
-      </c>
-      <c r="C12" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
-        <v>4</v>
-      </c>
-      <c r="C13" s="2">
-        <v>21</v>
-      </c>
+      <c r="C11" s="1">
+        <f>AVERAGE(C2:C8)</f>
+        <v>21.5714285714286</v>
+      </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1353,65 +1350,65 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
+      <c r="A16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>4</v>
+      </c>
+      <c r="C16" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>4</v>
+      </c>
+      <c r="C17" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>5</v>
       </c>
       <c r="C18" s="2">
-        <f>AVERAGE(C11:C15)</f>
-        <v>19.8</v>
-      </c>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="3">
-        <v>3</v>
-      </c>
-      <c r="C21" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="3">
-        <v>4</v>
-      </c>
-      <c r="C22" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
+      <c r="A21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="3">
-        <v>4</v>
-      </c>
-      <c r="C23" s="3">
-        <v>18</v>
+      <c r="C21" s="2">
+        <f>AVERAGE(C14:C18)</f>
+        <v>21.4</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1419,10 +1416,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1430,10 +1427,10 @@
         <v>19</v>
       </c>
       <c r="B25" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C25" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1441,10 +1438,10 @@
         <v>20</v>
       </c>
       <c r="B26" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1459,14 +1456,14 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C21:C26)</f>
-        <v>19.8333333333333</v>
+        <f>AVERAGE(C24:C26)</f>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1477,8 +1474,8 @@
         <v>23</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C5,C11:C15,C21:C26)</f>
-        <v>20.2666666666667</v>
+        <f>AVERAGE(C2:C8,C14:C18,C24:C26)</f>
+        <v>21.4</v>
       </c>
     </row>
   </sheetData>
@@ -1517,7 +1514,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1528,7 +1525,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1536,99 +1533,99 @@
         <v>26</v>
       </c>
       <c r="B4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1">
-        <v>22</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1">
-        <v>12</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1">
+        <f>AVERAGE(C2:C4)</f>
+        <v>23.6666666666667</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="2">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="2">
+        <v>3</v>
+      </c>
+      <c r="C11" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="1">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="B12" s="2">
+        <v>4</v>
+      </c>
+      <c r="C12" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="1">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="B13" s="2">
+        <v>4</v>
+      </c>
+      <c r="C13" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="1">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1">
+      <c r="B14" s="2">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="1">
-        <f>AVERAGE(C2:C9)</f>
-        <v>19.625</v>
-      </c>
-      <c r="D12" s="2"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1636,22 +1633,16 @@
         <v>33</v>
       </c>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="2">
-        <v>4</v>
-      </c>
-      <c r="C17" s="2">
-        <v>21</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2"/>
@@ -1659,20 +1650,26 @@
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C15:C17)</f>
-        <v>21.6666666666667</v>
+      <c r="A19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="2">
+        <f>AVERAGE(C10:C16)</f>
+        <v>17.7142857142857</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="3">
+        <v>3</v>
+      </c>
+      <c r="C22" s="3">
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1680,10 +1677,10 @@
         <v>35</v>
       </c>
       <c r="B23" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1694,7 +1691,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1702,10 +1699,10 @@
         <v>37</v>
       </c>
       <c r="B25" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1713,10 +1710,10 @@
         <v>38</v>
       </c>
       <c r="B26" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" s="3">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1731,14 +1728,14 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C23:C26)</f>
-        <v>18.25</v>
+        <f>AVERAGE(C22:C26)</f>
+        <v>20.4</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1749,8 +1746,8 @@
         <v>39</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C9,C15:C17,C23:C26)</f>
-        <v>19.6666666666667</v>
+        <f>AVERAGE(C2:C4,C10:C16,C22:C26)</f>
+        <v>19.8</v>
       </c>
     </row>
   </sheetData>
@@ -1762,7 +1759,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1789,7 +1786,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1800,7 +1797,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1811,7 +1808,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1822,7 +1819,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1833,7 +1830,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1841,10 +1838,10 @@
         <v>45</v>
       </c>
       <c r="B7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1866,7 +1863,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1877,7 +1874,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1888,19 +1885,13 @@
         <v>5</v>
       </c>
       <c r="C11" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="1">
-        <v>5</v>
-      </c>
-      <c r="C12" s="1">
-        <v>21</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1"/>
@@ -1908,32 +1899,38 @@
       <c r="C13" s="1"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="1">
-        <f>AVERAGE(C2:C12)</f>
-        <v>20.5454545454545</v>
-      </c>
-      <c r="D15" s="2"/>
+      <c r="A14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="1">
+        <f>AVERAGE(C2:C11)</f>
+        <v>20.5</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="2">
+        <v>4</v>
+      </c>
+      <c r="C17" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B18" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C18" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1948,13 +1945,13 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C21" s="2">
-        <f>AVERAGE(C18:C18)</f>
+        <f>AVERAGE(C17:C18)</f>
         <v>21</v>
       </c>
     </row>
@@ -1977,7 +1974,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1985,22 +1982,16 @@
         <v>54</v>
       </c>
       <c r="B26" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C26" s="3">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" s="3">
-        <v>6</v>
-      </c>
-      <c r="C27" s="3">
-        <v>21</v>
-      </c>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3"/>
@@ -2008,32 +1999,27 @@
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="A29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="3">
-        <f>AVERAGE(C24:C27)</f>
-        <v>16.25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
+      <c r="C29" s="3">
+        <f>AVERAGE(C24:C26)</f>
+        <v>15.3333333333333</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="4">
-        <f>AVERAGE(C2:C12,C18:C18,C24:C27)</f>
-        <v>19.5</v>
+      <c r="B32" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C11,C17:C18,C24:C26)</f>
+        <v>19.5333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2066,7 +2052,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -2077,35 +2063,35 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2120,44 +2106,42 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1">
         <f>AVERAGE(C2:C5)</f>
-        <v>22.75</v>
+        <v>19.75</v>
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" customFormat="1"/>
-    <row r="10" customFormat="1"/>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B13" s="2">
         <v>2</v>
@@ -2168,7 +2152,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
@@ -2179,62 +2163,62 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B16" s="2">
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B17" s="2">
         <v>3</v>
       </c>
       <c r="C17" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B18" s="2">
         <v>3</v>
       </c>
       <c r="C18" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B19" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B20" s="2">
         <v>7</v>
@@ -2255,21 +2239,19 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C23" s="2">
         <f>AVERAGE(C11:C20)</f>
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="24" customFormat="1"/>
-    <row r="25" customFormat="1"/>
+        <v>18.7</v>
+      </c>
+    </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B26" s="3">
         <v>5</v>
@@ -2290,7 +2272,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>21</v>
@@ -2300,18 +2282,16 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" customFormat="1"/>
-    <row r="31" customFormat="1"/>
     <row r="32" customFormat="1" spans="1:3">
       <c r="A32" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C5,C11:C20,C26:C26)</f>
-        <v>19.2</v>
+        <v>18.5333333333333</v>
       </c>
     </row>
   </sheetData>
